--- a/Divergencias_DN700_022-007300.xlsx
+++ b/Divergencias_DN700_022-007300.xlsx
@@ -1346,12 +1346,12 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>007343, 007344, 007350, 007301</t>
+          <t>007343, 007344, 007350</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Numeração das notas repetida (item "2" duas vezes; 007301 sem nota 2 nas 007304/05/06 etc.).</t>
+          <t>Numeração das notas repetida (item "2" aparece duas vezes, faltando o 3).</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
